--- a/ig/main/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/main/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2707" uniqueCount="2705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2737" uniqueCount="2735">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260730120000</t>
+    <t>20260928120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:00:00+01:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -834,7 +834,7 @@
     <t>0216</t>
   </si>
   <si>
-    <t>Gamma-angiographie cardiaque, tomographie cavitaire (fonctions ventriculaires, bilan de rythmologie)</t>
+    <t>Exploration en médecine nucléaire mesure de la fraction éjection ventriculaire</t>
   </si>
   <si>
     <t>0217</t>
@@ -1080,7 +1080,7 @@
     <t>0278</t>
   </si>
   <si>
-    <t>Lymphoscintigraphie</t>
+    <t>Exploration diagnostique par lymphoscintigraphie incluant recherche de ganglion sentinelle (GLS)</t>
   </si>
   <si>
     <t>0284</t>
@@ -1446,13 +1446,13 @@
     <t>0426</t>
   </si>
   <si>
-    <t>Scintigraphie au 18F-choline (suivi cancer de prostate)</t>
+    <t>Exploration diagnostique par TEP PSMA pour cancer de la prostate</t>
   </si>
   <si>
     <t>0427</t>
   </si>
   <si>
-    <t>Scintigraphie au 18F-DOPA (explorations tumeur endocrine)</t>
+    <t>Exploration diagnostique scintigraphique ou TEP paragangliome, phéochromocytome, tumeur endocrine</t>
   </si>
   <si>
     <t>0428</t>
@@ -1464,25 +1464,25 @@
     <t>0429</t>
   </si>
   <si>
-    <t>Scintigraphie rénale</t>
+    <t>Exploration diagnostique scintigraphique rénale</t>
   </si>
   <si>
     <t>0430</t>
   </si>
   <si>
-    <t>Scintigraphie au MIBG</t>
+    <t>Exploration diagnostique scintigraphique au MIBG</t>
   </si>
   <si>
     <t>0431</t>
   </si>
   <si>
-    <t>Scintigraphie aux hématies marquées (recherche de saignement)</t>
+    <t>Exploration diagnostique scintigraphique aux hématies marquées (recherche de saignement)</t>
   </si>
   <si>
     <t>0432</t>
   </si>
   <si>
-    <t>Scintigraphie de la neurotransmission dopaminergique (Dat-scan)</t>
+    <t>Exploration diagnostique scintigraphique ou TEP de la neurotransmission dopaminergique par Dat-scan ou F-DOPA (Syndrome Parkinsonien)</t>
   </si>
   <si>
     <t>0433</t>
@@ -1494,7 +1494,7 @@
     <t>0434</t>
   </si>
   <si>
-    <t>Scintigraphie de perfusion avec test au Captopril (bilan HTA rénovasculaire) et au Lasilix (bilan des obstacles des voies excrétrices urinaires)</t>
+    <t>Exploration diagnostique scintigraphique rénale de perfusion avec test médicamenteux pour recherche d'une HTA</t>
   </si>
   <si>
     <t>0435</t>
@@ -1506,13 +1506,13 @@
     <t>0436</t>
   </si>
   <si>
-    <t>Scintigraphie myocardique à l'effort ou pharmacologique</t>
+    <t>Exploration diagnostique scintigraphique de perfusion myocardique à l'effort ou après stress pharmacologique (99mTc/201Tl)</t>
   </si>
   <si>
     <t>0437</t>
   </si>
   <si>
-    <t>Scintigraphie SPECT-CT</t>
+    <t>Exploration diagnostique scintigraphique ventilation perfusion pulmonaire</t>
   </si>
   <si>
     <t>0441</t>
@@ -2676,7 +2676,7 @@
     <t>0720</t>
   </si>
   <si>
-    <t>Scintigraphie osseuse</t>
+    <t>Exploration diagnostique scintigraphique osseuse</t>
   </si>
   <si>
     <t>0721</t>
@@ -2733,6 +2733,12 @@
     <t>Suivi de grossesse à risque</t>
   </si>
   <si>
+    <t>0731</t>
+  </si>
+  <si>
+    <t>Surveillance du nouveau-né à risque</t>
+  </si>
+  <si>
     <t>0732</t>
   </si>
   <si>
@@ -5643,12 +5649,6 @@
     <t>Téléexpertise en moins de 7 jours</t>
   </si>
   <si>
-    <t>1273</t>
-  </si>
-  <si>
-    <t>Téléexpertise en plus de 7 jours</t>
-  </si>
-  <si>
     <t>1274</t>
   </si>
   <si>
@@ -6594,7 +6594,7 @@
     <t>1447</t>
   </si>
   <si>
-    <t>Prescription de vaccin</t>
+    <t>Prescription de vaccins selon le calendrier vaccinal de l'adolescent et de l'adulte</t>
   </si>
   <si>
     <t>1448</t>
@@ -7110,19 +7110,19 @@
     <t>1535</t>
   </si>
   <si>
-    <t>Vaccination du calendrier vaccinal de l’adolescent et de l’adulte</t>
+    <t>Vaccination selon le calendrier vaccinal de l'adolescent et de l'adulte</t>
   </si>
   <si>
     <t>1536</t>
   </si>
   <si>
-    <t>Vaccination du calendrier vaccinal du jeune enfant (0-12 ans)</t>
+    <t>Vaccination selon le calendrier vaccinal du jeune enfant (0-12 ans)</t>
   </si>
   <si>
     <t>1537</t>
   </si>
   <si>
-    <t>Vaccination du calendrier vaccinal du sénior</t>
+    <t>Vaccination selon le calendrier vaccinal du sénior</t>
   </si>
   <si>
     <t>1538</t>
@@ -7644,13 +7644,7 @@
     <t>1624</t>
   </si>
   <si>
-    <t>Contention nocturne</t>
-  </si>
-  <si>
-    <t>1625</t>
-  </si>
-  <si>
-    <t>Soin de pédicurie</t>
+    <t>Création de contention nocturne</t>
   </si>
   <si>
     <t>1626</t>
@@ -7830,7 +7824,7 @@
     <t>1655</t>
   </si>
   <si>
-    <t>Evaluation visuelle des troubles orthoptiques et neurovisuels dans le cadre des troubles du neuro-développement (TNV - TND)</t>
+    <t>Evaluation orthoptique et/ou prise en soins de la fonction visuelle et neurovisuelle dans le cadre du neurodéveloppement (TNV - TND)</t>
   </si>
   <si>
     <t>1656</t>
@@ -7842,7 +7836,7 @@
     <t>1657</t>
   </si>
   <si>
-    <t>Bilan visuel dans le cadre d'un renouvellement ou d'une adaptation de la correction optique (Protocole de coopération Renouvellement d'Optique (RNO))</t>
+    <t>Bilan visuel dans le cadre d'un renouvellement ou d'une adaptation de la correction optique (Protocole de coopération Renouvellement d'Optique (RNO))</t>
   </si>
   <si>
     <t>1658</t>
@@ -7878,7 +7872,7 @@
     <t>1663</t>
   </si>
   <si>
-    <t>Evaluation oculométrique par enregistrement – technique d'Eye tracking</t>
+    <t>Evaluation oculométrique par enregistrement - technique d'Eye tracking</t>
   </si>
   <si>
     <t>1664</t>
@@ -7980,7 +7974,7 @@
     <t>1680</t>
   </si>
   <si>
-    <t>Autorisation par l’ARS pour la sous-traitance de préparation pharmaceutique</t>
+    <t>Autorisation par l'ARS pour la sous-traitance de préparation pharmaceutique présentant un risque pour la santé</t>
   </si>
   <si>
     <t>1681</t>
@@ -8119,6 +8113,102 @@
   </si>
   <si>
     <t>Groupe (ou stage) psycho-éducatif de responsabilisation pour prévention de la violence et/ou de sa récidive</t>
+  </si>
+  <si>
+    <t>1704</t>
+  </si>
+  <si>
+    <t>Exploration diagnostique scintigraphique pour patient dialysé</t>
+  </si>
+  <si>
+    <t>1705</t>
+  </si>
+  <si>
+    <t>Exploration diagnostique par TEP 18F-FDG pour pathologie neurologique (démence, épilepsie, Parkinson, AVC)</t>
+  </si>
+  <si>
+    <t>1706</t>
+  </si>
+  <si>
+    <t>Exploration diagnostique par TEP pour des plaques amyloïdes</t>
+  </si>
+  <si>
+    <t>1707</t>
+  </si>
+  <si>
+    <t>Exploration diagnostique scintigraphique ou TEP de pathologie thyroïdienne ou parathyroïdienne</t>
+  </si>
+  <si>
+    <t>1708</t>
+  </si>
+  <si>
+    <t>Exploration diagnostique scintigraphique ou TEP de pathologie surrénalienne</t>
+  </si>
+  <si>
+    <t>1709</t>
+  </si>
+  <si>
+    <t>Traitement de médecine nucléaire / RIV par 131I des pathologies bénignes de la thyroïde</t>
+  </si>
+  <si>
+    <t>1710</t>
+  </si>
+  <si>
+    <t>Traitement de médecine nucléaire / RIV  par lutetium-177 oxodotreotide pour Tumeur neuroendocrine - TNE</t>
+  </si>
+  <si>
+    <t>1711</t>
+  </si>
+  <si>
+    <t>Traitement de médecine nucléaire / RIV  par lutetium-177 PSMA pour cancer de la prostate</t>
+  </si>
+  <si>
+    <t>1712</t>
+  </si>
+  <si>
+    <t>Traitement de médecine nucléaire / RIV par radium-223 pour cancer de la prostate avec métastases osseuses</t>
+  </si>
+  <si>
+    <t>1713</t>
+  </si>
+  <si>
+    <t>Traitement de médecine nucléaire / RIV  par 90Y microsphères pour cancer hépatocellulaire (CHC) et lésion secondaire hépatique</t>
+  </si>
+  <si>
+    <t>1714</t>
+  </si>
+  <si>
+    <t>Traitement de médecine nucléaire / RIV  par 131I pour cancer de la thyroïde</t>
+  </si>
+  <si>
+    <t>1715</t>
+  </si>
+  <si>
+    <t>Prise en charge médecine nucléaire pédiatrique (0 - 5 ans)</t>
+  </si>
+  <si>
+    <t>1716</t>
+  </si>
+  <si>
+    <t>Exploration diagnostique scintigraphique splénique ou hépatosplénique</t>
+  </si>
+  <si>
+    <t>1717</t>
+  </si>
+  <si>
+    <t>Exploration diagnostique scintigraphique des glandes salivaires</t>
+  </si>
+  <si>
+    <t>1718</t>
+  </si>
+  <si>
+    <t>Exploration diagnostique scintigraphique aux leucocytes marqués pour recherche d'infection</t>
+  </si>
+  <si>
+    <t>1719</t>
+  </si>
+  <si>
+    <t>Recherche en oncologie, bilan d'extension</t>
   </si>
   <si>
     <t/>
@@ -8389,7 +8479,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1340"/>
+  <dimension ref="A1:B1355"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -19105,15 +19195,135 @@
         <v>2702</v>
       </c>
       <c r="B1339" t="s" s="2">
-        <v>2702</v>
+        <v>2703</v>
       </c>
     </row>
     <row r="1340">
       <c r="A1340" t="s" s="2">
-        <v>2703</v>
+        <v>2704</v>
       </c>
       <c r="B1340" t="s" s="2">
-        <v>2704</v>
+        <v>2705</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="s" s="2">
+        <v>2706</v>
+      </c>
+      <c r="B1341" t="s" s="2">
+        <v>2707</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="s" s="2">
+        <v>2708</v>
+      </c>
+      <c r="B1342" t="s" s="2">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="s" s="2">
+        <v>2710</v>
+      </c>
+      <c r="B1343" t="s" s="2">
+        <v>2711</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="s" s="2">
+        <v>2712</v>
+      </c>
+      <c r="B1344" t="s" s="2">
+        <v>2713</v>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="s" s="2">
+        <v>2714</v>
+      </c>
+      <c r="B1345" t="s" s="2">
+        <v>2715</v>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="s" s="2">
+        <v>2716</v>
+      </c>
+      <c r="B1346" t="s" s="2">
+        <v>2717</v>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="s" s="2">
+        <v>2718</v>
+      </c>
+      <c r="B1347" t="s" s="2">
+        <v>2719</v>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="s" s="2">
+        <v>2720</v>
+      </c>
+      <c r="B1348" t="s" s="2">
+        <v>2721</v>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="s" s="2">
+        <v>2722</v>
+      </c>
+      <c r="B1349" t="s" s="2">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="s" s="2">
+        <v>2724</v>
+      </c>
+      <c r="B1350" t="s" s="2">
+        <v>2725</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="s" s="2">
+        <v>2726</v>
+      </c>
+      <c r="B1351" t="s" s="2">
+        <v>2727</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="s" s="2">
+        <v>2728</v>
+      </c>
+      <c r="B1352" t="s" s="2">
+        <v>2729</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="s" s="2">
+        <v>2730</v>
+      </c>
+      <c r="B1353" t="s" s="2">
+        <v>2731</v>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="s" s="2">
+        <v>2732</v>
+      </c>
+      <c r="B1354" t="s" s="2">
+        <v>2732</v>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="s" s="2">
+        <v>2733</v>
+      </c>
+      <c r="B1355" t="s" s="2">
+        <v>2734</v>
       </c>
     </row>
   </sheetData>
